--- a/New folder/Dyeing_lead_time_new/Output_files/Output_all_together.xlsx
+++ b/New folder/Dyeing_lead_time_new/Output_files/Output_all_together.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M255"/>
+  <dimension ref="A1:M251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ST00381/26</t>
+          <t>ST00380/26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ST0038112N</t>
+          <t>ST0038033N</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
@@ -900,14 +900,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S50583</t>
+          <t>S14075</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>7.65</v>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>6.79</v>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -915,28 +917,24 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7.65</v>
+        <v>0.86</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ST00381/26</t>
+          <t>ST00380/26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ST0038129N</t>
+          <t>ST0038049N</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
@@ -949,14 +947,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S50403</t>
+          <t>S17245</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>7.65</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>6.98</v>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -964,18 +964,14 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>7.65</v>
+        <v>0.67</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -985,7 +981,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ST0038139N</t>
+          <t>ST0038112N</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
@@ -998,7 +994,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S50696</t>
+          <t>S50583</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1034,7 +1030,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ST0038140N</t>
+          <t>ST0038129N</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
@@ -1047,16 +1043,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S50717</t>
+          <t>S50403</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>7.65</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>6.87</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -1064,14 +1058,18 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.78</v>
+        <v>7.65</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1081,7 +1079,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ST0038146N</t>
+          <t>ST0038139N</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
@@ -1094,7 +1092,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S50868</t>
+          <t>S50696</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1125,16 +1123,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ST00440/26</t>
+          <t>ST00381/26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ST0044002N</t>
+          <t>ST0038140N</t>
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1143,14 +1141,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S01028</t>
+          <t>S50717</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14.78</v>
+        <v>7.65</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>6.87</v>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -1158,32 +1158,28 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14.78</v>
+        <v>0.78</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ST00440/26</t>
+          <t>ST00381/26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ST0044003N</t>
+          <t>ST0038144N</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1192,14 +1188,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S01216</t>
+          <t>S56979</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14.78</v>
+        <v>7.65</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>6.98</v>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -1207,32 +1205,28 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>14.78</v>
+        <v>0.67</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ST00440/26</t>
+          <t>ST00381/26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ST0044005N</t>
+          <t>ST0038146N</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1241,11 +1235,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S50584</t>
+          <t>S50868</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>14.78</v>
+        <v>7.65</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1256,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>14.78</v>
+        <v>7.65</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1265,23 +1259,23 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ST00440/26</t>
+          <t>ST00381/26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ST0044006N</t>
+          <t>ST0038154N</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1290,14 +1284,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S50712</t>
+          <t>S60663</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>14.78</v>
+        <v>7.65</v>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>7.01</v>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -1305,32 +1301,28 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>14.78</v>
+        <v>0.64</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ST00440/26</t>
+          <t>ST00381/26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ST0044007N</t>
+          <t>ST0038155N</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1339,14 +1331,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S00410</t>
+          <t>S60365</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14.78</v>
+        <v>7.65</v>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>6.9</v>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -1354,32 +1348,28 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>14.78</v>
+        <v>0.75</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ST00440/26</t>
+          <t>ST00401/26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ST0044008N</t>
+          <t>ST0040104N</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46271</v>
+        <v>46259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1388,14 +1378,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S00730</t>
+          <t>S01160</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>14.78</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>13.65</v>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -1403,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>14.78</v>
+        <v>1.13</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1412,7 +1404,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1416,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ST0044009N</t>
+          <t>ST0044001N</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
@@ -1437,14 +1429,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S01930</t>
+          <t>S01111</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>14.78</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>14.06</v>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -1452,18 +1446,14 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>14.78</v>
+        <v>0.72</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1473,7 +1463,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ST0044010N</t>
+          <t>ST0044002N</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
@@ -1486,7 +1476,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S05619</t>
+          <t>S01028</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1522,7 +1512,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ST0044011N</t>
+          <t>ST0044003N</t>
         </is>
       </c>
       <c r="C23" s="1" t="n">
@@ -1535,14 +1525,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S50934</t>
+          <t>S01216</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>14.78</v>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>13.77</v>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -1550,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>14.78</v>
+        <v>1.01</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1559,7 +1551,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1563,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ST0044012N</t>
+          <t>ST0044004N</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
@@ -1584,14 +1576,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S50677</t>
+          <t>S50452</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>14.78</v>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>13.9</v>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -1599,18 +1593,14 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>14.78</v>
+        <v>0.88</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1620,7 +1610,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ST0044013N</t>
+          <t>ST0044005N</t>
         </is>
       </c>
       <c r="C25" s="1" t="n">
@@ -1633,7 +1623,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S50480</t>
+          <t>S50584</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1669,7 +1659,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ST0044014N</t>
+          <t>ST0044006N</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
@@ -1682,7 +1672,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S50703</t>
+          <t>S50712</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1718,7 +1708,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ST0044015N</t>
+          <t>ST0044007N</t>
         </is>
       </c>
       <c r="C27" s="1" t="n">
@@ -1731,14 +1721,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S00445</t>
+          <t>S00410</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>14.78</v>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>14.05</v>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -1746,18 +1738,14 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>14.78</v>
+        <v>0.73</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1767,7 +1755,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ST0044016N</t>
+          <t>ST0044008N</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
@@ -1780,7 +1768,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S17249</t>
+          <t>S00730</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1816,7 +1804,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ST0044017N</t>
+          <t>ST0044009N</t>
         </is>
       </c>
       <c r="C29" s="1" t="n">
@@ -1829,14 +1817,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S00294</t>
+          <t>S01930</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>14.78</v>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>14.06</v>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -1844,18 +1834,14 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>14.78</v>
+        <v>0.72</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1865,7 +1851,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ST0044018N</t>
+          <t>ST0044010N</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
@@ -1878,18 +1864,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S01010</t>
+          <t>S05619</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>14.78</v>
       </c>
-      <c r="G30" t="n">
-        <v>14</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -1897,14 +1879,18 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.78</v>
+        <v>14.78</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1914,7 +1900,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ST0044019N</t>
+          <t>ST0044011N</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
@@ -1927,7 +1913,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S17261</t>
+          <t>S50934</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1963,7 +1949,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ST0044020N</t>
+          <t>ST0044012N</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
@@ -1976,7 +1962,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S50986</t>
+          <t>S50677</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2012,7 +1998,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ST0044021N</t>
+          <t>ST0044013N</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
@@ -2025,7 +2011,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S51830</t>
+          <t>S50480</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2061,7 +2047,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ST0044022N</t>
+          <t>ST0044014N</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
@@ -2074,7 +2060,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S50661</t>
+          <t>S50703</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2110,7 +2096,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ST0044023N</t>
+          <t>ST0044015N</t>
         </is>
       </c>
       <c r="C35" s="1" t="n">
@@ -2123,7 +2109,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S50967</t>
+          <t>S00445</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2159,7 +2145,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ST0044024N</t>
+          <t>ST0044016N</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
@@ -2172,7 +2158,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S16310</t>
+          <t>S17249</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2208,7 +2194,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ST0044025N</t>
+          <t>ST0044017N</t>
         </is>
       </c>
       <c r="C37" s="1" t="n">
@@ -2221,7 +2207,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S50516</t>
+          <t>S00294</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2257,7 +2243,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ST0044027N</t>
+          <t>ST0044018N</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
@@ -2270,14 +2256,16 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S16065</t>
+          <t>S01010</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>14.78</v>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>13.89</v>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -2285,28 +2273,24 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>14.78</v>
+        <v>0.89</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ST0044101N</t>
+          <t>ST0044019N</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
@@ -2319,11 +2303,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S05220</t>
+          <t>S17261</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20.4</v>
+        <v>14.78</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -2334,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>20.4</v>
+        <v>14.78</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2350,12 +2334,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ST0044102N</t>
+          <t>ST0044020N</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
@@ -2368,11 +2352,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S01577</t>
+          <t>S50986</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13.6</v>
+        <v>14.78</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -2383,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>13.6</v>
+        <v>14.78</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2399,12 +2383,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ST0044105N</t>
+          <t>ST0044021N</t>
         </is>
       </c>
       <c r="C41" s="1" t="n">
@@ -2417,15 +2401,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S00700</t>
+          <t>S51830</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7.65</v>
+        <v>14.78</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>6.84</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2434,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2446,12 +2430,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ST0044106N</t>
+          <t>ST0044022N</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
@@ -2464,14 +2448,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S00794</t>
+          <t>S50661</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>13.6</v>
+        <v>14.78</v>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>14.08</v>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -2479,28 +2465,24 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>13.6</v>
+        <v>0.7</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ST0044107N</t>
+          <t>ST0044023N</t>
         </is>
       </c>
       <c r="C43" s="1" t="n">
@@ -2513,18 +2495,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S50701</t>
+          <t>S50967</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>42</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
+        <v>14.78</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -2532,24 +2510,28 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>14.78</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ST0044108N</t>
+          <t>ST0044024N</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
@@ -2562,11 +2544,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S00090</t>
+          <t>S16310</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20.4</v>
+        <v>14.78</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -2577,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>20.4</v>
+        <v>14.78</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2593,12 +2575,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ST0044110N</t>
+          <t>ST0044025N</t>
         </is>
       </c>
       <c r="C45" s="1" t="n">
@@ -2611,11 +2593,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S00093</t>
+          <t>S50516</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7.65</v>
+        <v>14.78</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -2626,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7.65</v>
+        <v>14.78</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2635,19 +2617,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ST0044111N</t>
+          <t>ST0044026N</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
@@ -2660,14 +2642,16 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S01912</t>
+          <t>S53132</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>13.6</v>
+        <v>14.78</v>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>13.83</v>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -2675,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>13.6</v>
+        <v>0.95</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2684,19 +2668,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ST00441/26</t>
+          <t>ST00440/26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ST0044113N</t>
+          <t>ST0044027N</t>
         </is>
       </c>
       <c r="C47" s="1" t="n">
@@ -2709,11 +2693,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S05619</t>
+          <t>S16065</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>13.6</v>
+        <v>14.78</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -2724,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>13.6</v>
+        <v>14.78</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2745,7 +2729,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ST0044114N</t>
+          <t>ST0044101N</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
@@ -2758,7 +2742,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S50430</t>
+          <t>S05220</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2794,7 +2778,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ST0044115N</t>
+          <t>ST0044102N</t>
         </is>
       </c>
       <c r="C49" s="1" t="n">
@@ -2807,16 +2791,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S50484</t>
+          <t>S01577</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>7.65</v>
+        <v>13.6</v>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
-        <v>6.93</v>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -2824,14 +2806,18 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.72</v>
+        <v>13.6</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2841,7 +2827,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ST0044116N</t>
+          <t>ST0044105N</t>
         </is>
       </c>
       <c r="C50" s="1" t="n">
@@ -2854,14 +2840,16 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S00072</t>
+          <t>S00700</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>13.6</v>
+        <v>7.65</v>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>6.84</v>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -2869,18 +2857,14 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>13.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2890,7 +2874,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ST0044117N</t>
+          <t>ST0044107N</t>
         </is>
       </c>
       <c r="C51" s="1" t="n">
@@ -2903,14 +2887,16 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S00267</t>
+          <t>S50701</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>13.6</v>
+        <v>42.5</v>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>41.69</v>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -2918,18 +2904,14 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>13.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2939,7 +2921,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ST0044118N</t>
+          <t>ST0044109N</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
@@ -2952,14 +2934,16 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S00654</t>
+          <t>S01012</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>13.6</v>
+        <v>55.93</v>
       </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>55.47</v>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -2967,18 +2951,14 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>13.6</v>
+        <v>0.46</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2988,7 +2968,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ST0044119N</t>
+          <t>ST0044110N</t>
         </is>
       </c>
       <c r="C53" s="1" t="n">
@@ -3001,11 +2981,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S50967</t>
+          <t>S00093</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>13.6</v>
+        <v>7.65</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -3016,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>13.6</v>
+        <v>7.65</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3025,7 +3005,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3017,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ST0044121N</t>
+          <t>ST0044113N</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
@@ -3050,7 +3030,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S01249</t>
+          <t>S05619</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -3081,12 +3061,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00441/26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ST0044401N</t>
+          <t>ST0044114N</t>
         </is>
       </c>
       <c r="C55" s="1" t="n">
@@ -3099,7 +3079,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S01577</t>
+          <t>S50430</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3130,12 +3110,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00441/26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ST0044402N</t>
+          <t>ST0044115N</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
@@ -3148,14 +3128,16 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S00386</t>
+          <t>S50484</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>20.4</v>
+        <v>7.65</v>
       </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>6.93</v>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -3163,28 +3145,24 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>20.4</v>
+        <v>0.72</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00441/26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ST0044404N</t>
+          <t>ST0044117N</t>
         </is>
       </c>
       <c r="C57" s="1" t="n">
@@ -3197,11 +3175,11 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S01600</t>
+          <t>S00267</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>20.4</v>
+        <v>13.6</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -3212,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>20.4</v>
+        <v>13.6</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3228,12 +3206,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00441/26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ST0044405N</t>
+          <t>ST0044119N</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
@@ -3246,11 +3224,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S00227</t>
+          <t>S50967</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>20.4</v>
+        <v>13.6</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -3261,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>20.4</v>
+        <v>13.6</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3277,12 +3255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00441/26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ST0044406N</t>
+          <t>ST0044120N</t>
         </is>
       </c>
       <c r="C59" s="1" t="n">
@@ -3295,7 +3273,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S00074</t>
+          <t>S53132</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -3303,7 +3281,7 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>6.98</v>
+        <v>6.82</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -3312,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3324,12 +3302,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00441/26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ST0044409N</t>
+          <t>ST0044121N</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
@@ -3342,16 +3320,14 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S00222</t>
+          <t>S01249</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7.65</v>
+        <v>13.6</v>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>6.87</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -3359,24 +3335,28 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.78</v>
+        <v>13.6</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ST00444/26</t>
+          <t>ST00443/26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ST0044410N</t>
+          <t>ST0044301N</t>
         </is>
       </c>
       <c r="C61" s="1" t="n">
@@ -3389,15 +3369,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S00094</t>
+          <t>S01029</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>7.65</v>
+        <v>38.5</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>7.01</v>
+        <v>34.95</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3406,14 +3386,18 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.64</v>
+        <v>3.55</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3423,7 +3407,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ST0044412N</t>
+          <t>ST0044401N</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
@@ -3436,16 +3420,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S14110</t>
+          <t>S01577</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7.65</v>
+        <v>20.4</v>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>7.07</v>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -3453,14 +3435,18 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.58</v>
+        <v>20.4</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3470,7 +3456,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ST0044413N</t>
+          <t>ST0044402N</t>
         </is>
       </c>
       <c r="C63" s="1" t="n">
@@ -3483,7 +3469,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S50633</t>
+          <t>S00386</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3519,7 +3505,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ST0044414N</t>
+          <t>ST0044404N</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
@@ -3532,7 +3518,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S50063</t>
+          <t>S01600</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3568,7 +3554,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ST0044415N</t>
+          <t>ST0044405N</t>
         </is>
       </c>
       <c r="C65" s="1" t="n">
@@ -3581,16 +3567,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S50525</t>
+          <t>S00227</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7.65</v>
+        <v>20.4</v>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
-        <v>6.88</v>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -3598,14 +3582,18 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.77</v>
+        <v>20.4</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3615,7 +3603,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ST0044416N</t>
+          <t>ST0044406N</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
@@ -3628,7 +3616,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>S50440</t>
+          <t>S00074</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -3636,7 +3624,7 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>6.88</v>
+        <v>6.98</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -3645,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3662,7 +3650,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ST0044418N</t>
+          <t>ST0044409N</t>
         </is>
       </c>
       <c r="C67" s="1" t="n">
@@ -3675,7 +3663,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S00282</t>
+          <t>S00222</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -3683,7 +3671,7 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>7.06</v>
+        <v>6.87</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -3692,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3709,7 +3697,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ST0044419N</t>
+          <t>ST0044410N</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
@@ -3722,14 +3710,16 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S00657</t>
+          <t>S00094</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>20.4</v>
+        <v>7.65</v>
       </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>7.01</v>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -3737,18 +3727,14 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>20.4</v>
+        <v>0.64</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3758,7 +3744,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ST0044420N</t>
+          <t>ST0044412N</t>
         </is>
       </c>
       <c r="C69" s="1" t="n">
@@ -3771,7 +3757,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S16376</t>
+          <t>S14110</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -3779,7 +3765,7 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>6.91</v>
+        <v>7.07</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -3788,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3805,7 +3791,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ST0044421N</t>
+          <t>ST0044413N</t>
         </is>
       </c>
       <c r="C70" s="1" t="n">
@@ -3818,16 +3804,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S50571</t>
+          <t>S50633</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>7.65</v>
+        <v>20.4</v>
       </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>6.77</v>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -3835,24 +3819,28 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.88</v>
+        <v>20.4</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ST0044586N</t>
+          <t>ST0044414N</t>
         </is>
       </c>
       <c r="C71" s="1" t="n">
@@ -3865,16 +3853,14 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S00755</t>
+          <t>S50063</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>7.65</v>
+        <v>20.4</v>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>7.04</v>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -3882,24 +3868,28 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.61</v>
+        <v>20.4</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ST0044587N</t>
+          <t>ST0044415N</t>
         </is>
       </c>
       <c r="C72" s="1" t="n">
@@ -3912,14 +3902,16 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S16067</t>
+          <t>S50525</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>7.65</v>
       </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>6.88</v>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -3927,28 +3919,24 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>7.65</v>
+        <v>0.77</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ST0044588N</t>
+          <t>ST0044416N</t>
         </is>
       </c>
       <c r="C73" s="1" t="n">
@@ -3961,14 +3949,16 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S16304</t>
+          <t>S50440</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>7.65</v>
       </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>6.88</v>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -3976,28 +3966,24 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>7.65</v>
+        <v>0.77</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ST0044589N</t>
+          <t>ST0044418N</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
@@ -4010,43 +3996,41 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S50930</t>
+          <t>S00282</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6.93</v>
+        <v>7.65</v>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>7.06</v>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="K74" t="n">
-        <v>6.93</v>
+        <v>0.59</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ST0044590N</t>
+          <t>ST0044419N</t>
         </is>
       </c>
       <c r="C75" s="1" t="n">
@@ -4059,11 +4043,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S00862</t>
+          <t>S00657</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>7.65</v>
+        <v>20.4</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
@@ -4074,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>7.65</v>
+        <v>20.4</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4083,19 +4067,19 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ST0044591N</t>
+          <t>ST0044420N</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
@@ -4108,14 +4092,16 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S50706</t>
+          <t>S16376</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>7.65</v>
       </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>6.91</v>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -4123,28 +4109,24 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>7.65</v>
+        <v>0.74</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ST00445/26</t>
+          <t>ST00444/26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ST0044592N</t>
+          <t>ST0044421N</t>
         </is>
       </c>
       <c r="C77" s="1" t="n">
@@ -4157,47 +4139,45 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S54399</t>
+          <t>S50571</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6.93</v>
+        <v>7.65</v>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>6.77</v>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>6.77</v>
       </c>
       <c r="K77" t="n">
-        <v>6.93</v>
+        <v>0.88</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ST00231/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ST0023101N</t>
+          <t>ST0044586N</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46200</v>
+        <v>46271</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4206,51 +4186,45 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KS-BLACK</t>
+          <t>S00755</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1005.8</v>
-      </c>
-      <c r="G78" t="n">
-        <v>111.28</v>
-      </c>
+        <v>7.65</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>527.49</v>
+        <v>7.04</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>204.34</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>367.03</v>
+        <v>0.61</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>more_than_48p</t>
-        </is>
-      </c>
+          <t>2/57 SPUN POLYSTER YARN</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ST00319/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ST0031907N</t>
+          <t>ST0044587N</t>
         </is>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46232</v>
+        <v>46271</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4259,11 +4233,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>D10038</t>
+          <t>S16067</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
@@ -4274,32 +4248,32 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
+          <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ST00319/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ST0031936N</t>
+          <t>ST0044588N</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46232</v>
+        <v>46271</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4308,11 +4282,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S05257</t>
+          <t>S16304</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -4323,32 +4297,32 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
+          <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ST00319/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ST0031977N</t>
+          <t>ST0044589N</t>
         </is>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46232</v>
+        <v>46271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4357,11 +4331,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S13189</t>
+          <t>S50930</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>13.91</v>
+        <v>6.93</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
@@ -4372,32 +4346,32 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>13.91</v>
+        <v>6.93</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
+          <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ST00350/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ST0035042N</t>
+          <t>ST0044590N</t>
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46241</v>
+        <v>46271</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4406,11 +4380,11 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S04334</t>
+          <t>S00862</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -4421,32 +4395,32 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
+          <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ST00354/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ST0035435N</t>
+          <t>ST0044591N</t>
         </is>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46243</v>
+        <v>46271</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4455,18 +4429,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SV7035</t>
+          <t>S50706</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
+        <v>7.65</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -4474,32 +4444,32 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>13.91</v>
+        <v>7.65</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
+          <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ST00392/26</t>
+          <t>ST00445/26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ST0039243N</t>
+          <t>ST0044592N</t>
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46258</v>
+        <v>46271</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -4508,11 +4478,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SV2436</t>
+          <t>S54399</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>13.91</v>
+        <v>6.93</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -4523,32 +4493,32 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>13.91</v>
+        <v>6.93</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
+          <t>2/57 SPUN POLYSTER YARN</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ST00402/26</t>
+          <t>ST00231/26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ST0040215N</t>
+          <t>ST0023101N</t>
         </is>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46260</v>
+        <v>46200</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4557,22 +4527,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SV0285</t>
+          <t>KS-BLACK</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>147.66</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+        <v>1005.8</v>
+      </c>
+      <c r="G85" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="H85" t="n">
+        <v>587.1</v>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>350.08</v>
       </c>
       <c r="K85" t="n">
-        <v>147.66</v>
+        <v>363.06</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4588,16 +4562,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ST00402/26</t>
+          <t>ST00319/26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ST0040217N</t>
+          <t>ST0031907N</t>
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46260</v>
+        <v>46232</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4606,11 +4580,11 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SV0613</t>
+          <t>D10038</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -4621,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4630,23 +4604,23 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ST00417/26</t>
+          <t>ST00319/26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ST0041702N</t>
+          <t>ST0031936N</t>
         </is>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46264</v>
+        <v>46232</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -4655,11 +4629,11 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SV0282</t>
+          <t>S05257</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
@@ -4670,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4679,23 +4653,23 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ST00418/26</t>
+          <t>ST00319/26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ST0041801N</t>
+          <t>ST0031977N</t>
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46265</v>
+        <v>46232</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4704,7 +4678,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S13019</t>
+          <t>S13189</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -4713,13 +4687,13 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>6.91</v>
+        <v>13.91</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4728,23 +4702,23 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00350/26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ST0043901N</t>
+          <t>ST0035042N</t>
         </is>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46271</v>
+        <v>46241</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4753,7 +4727,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>D10005</t>
+          <t>S04334</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -4784,16 +4758,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00354/26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ST0043904N</t>
+          <t>ST0035435N</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46271</v>
+        <v>46243</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4802,14 +4776,18 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SV9613</t>
+          <t>SV7035</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>27.82</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+        <v>13.91</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -4817,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4826,23 +4804,23 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00392/26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ST0043905N</t>
+          <t>ST0039243N</t>
         </is>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46271</v>
+        <v>46258</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4851,11 +4829,11 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S01925</t>
+          <t>SV2436</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>81.31999999999999</v>
+        <v>13.91</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -4866,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>81.31999999999999</v>
+        <v>13.91</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4875,23 +4853,23 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00402/26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ST0043906N</t>
+          <t>ST0040215N</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46271</v>
+        <v>46260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -4900,11 +4878,11 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>S00651</t>
+          <t>SV0285</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>13.91</v>
+        <v>147.66</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -4915,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>13.91</v>
+        <v>147.66</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4924,23 +4902,23 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00402/26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ST0043908N</t>
+          <t>ST0040217N</t>
         </is>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46271</v>
+        <v>46260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4949,7 +4927,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>S00052</t>
+          <t>SV0613</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -4980,16 +4958,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00417/26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ST0043912N</t>
+          <t>ST0041702N</t>
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4998,11 +4976,11 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>S13487</t>
+          <t>SV0282</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -5013,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5022,23 +5000,23 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ST00439/26</t>
+          <t>ST00418/26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ST0043913N</t>
+          <t>ST0041801N</t>
         </is>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46271</v>
+        <v>46265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5047,7 +5025,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>S09344</t>
+          <t>S13019</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5056,13 +5034,13 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>13.91</v>
+        <v>6.91</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5071,7 +5049,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5061,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ST0043918N</t>
+          <t>ST0043901N</t>
         </is>
       </c>
       <c r="C96" s="1" t="n">
@@ -5096,11 +5074,11 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>S16067</t>
+          <t>D10005</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -5111,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5120,7 +5098,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5110,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ST0043919N</t>
+          <t>ST0043904N</t>
         </is>
       </c>
       <c r="C97" s="1" t="n">
@@ -5145,7 +5123,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S16305</t>
+          <t>SV9613</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5181,7 +5159,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ST0043921N</t>
+          <t>ST0043905N</t>
         </is>
       </c>
       <c r="C98" s="1" t="n">
@@ -5194,11 +5172,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S50744</t>
+          <t>S01925</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>27.82</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
@@ -5209,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>27.82</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5218,7 +5196,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5208,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ST0043922N</t>
+          <t>ST0043906N</t>
         </is>
       </c>
       <c r="C99" s="1" t="n">
@@ -5243,7 +5221,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>S50937</t>
+          <t>S00651</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -5279,7 +5257,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ST0043923N</t>
+          <t>ST0043908N</t>
         </is>
       </c>
       <c r="C100" s="1" t="n">
@@ -5292,7 +5270,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>R0120</t>
+          <t>S00052</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -5328,7 +5306,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ST0043924N</t>
+          <t>ST0043912N</t>
         </is>
       </c>
       <c r="C101" s="1" t="n">
@@ -5341,16 +5319,14 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>S00170</t>
+          <t>S13487</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>81.31999999999999</v>
+        <v>13.91</v>
       </c>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="n">
-        <v>68.52</v>
-      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
         <v>0</v>
       </c>
@@ -5358,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>12.79999999999999</v>
+        <v>13.91</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5379,7 +5355,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ST0043925N</t>
+          <t>ST0043913N</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
@@ -5392,7 +5368,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SV6086</t>
+          <t>S09344</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -5428,7 +5404,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ST0043928N</t>
+          <t>ST0043918N</t>
         </is>
       </c>
       <c r="C103" s="1" t="n">
@@ -5441,11 +5417,11 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>S05292</t>
+          <t>S16067</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
@@ -5456,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5465,7 +5441,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5453,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ST0043931N</t>
+          <t>ST0043919N</t>
         </is>
       </c>
       <c r="C104" s="1" t="n">
@@ -5490,7 +5466,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SV7820</t>
+          <t>S16305</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -5526,7 +5502,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ST0043932N</t>
+          <t>ST0043921N</t>
         </is>
       </c>
       <c r="C105" s="1" t="n">
@@ -5539,11 +5515,11 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SV5144</t>
+          <t>S50744</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
@@ -5554,7 +5530,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5563,7 +5539,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5551,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ST0043933N</t>
+          <t>ST0043922N</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
@@ -5588,7 +5564,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SV4397</t>
+          <t>S50937</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -5624,7 +5600,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ST0043934N</t>
+          <t>ST0043923N</t>
         </is>
       </c>
       <c r="C107" s="1" t="n">
@@ -5637,7 +5613,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>S00445</t>
+          <t>R0120</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -5673,7 +5649,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ST0043935N</t>
+          <t>ST0043924N</t>
         </is>
       </c>
       <c r="C108" s="1" t="n">
@@ -5686,14 +5662,16 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>S00462</t>
+          <t>S00170</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>13.91</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>68.52</v>
+      </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
@@ -5701,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>13.91</v>
+        <v>12.79999999999999</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5722,7 +5700,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ST0043938N</t>
+          <t>ST0043925N</t>
         </is>
       </c>
       <c r="C109" s="1" t="n">
@@ -5735,11 +5713,11 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>QL103</t>
+          <t>SV6086</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
@@ -5750,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5759,7 +5737,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5749,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ST0043940N</t>
+          <t>ST0043928N</t>
         </is>
       </c>
       <c r="C110" s="1" t="n">
@@ -5784,7 +5762,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SV5823</t>
+          <t>S05292</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -5820,7 +5798,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ST0043941N</t>
+          <t>ST0043931N</t>
         </is>
       </c>
       <c r="C111" s="1" t="n">
@@ -5833,11 +5811,11 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>S00608</t>
+          <t>SV7820</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
@@ -5848,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5857,7 +5835,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5847,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ST0043942N</t>
+          <t>ST0043932N</t>
         </is>
       </c>
       <c r="C112" s="1" t="n">
@@ -5882,11 +5860,11 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>S01158</t>
+          <t>SV5144</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
@@ -5897,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5906,7 +5884,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5896,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ST0043947N</t>
+          <t>ST0043933N</t>
         </is>
       </c>
       <c r="C113" s="1" t="n">
@@ -5931,7 +5909,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>S01543</t>
+          <t>SV4397</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -5967,7 +5945,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ST0043948N</t>
+          <t>ST0043934N</t>
         </is>
       </c>
       <c r="C114" s="1" t="n">
@@ -5980,11 +5958,11 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>S00308</t>
+          <t>S00445</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
@@ -5995,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>13.91</v>
+        <v>27.82</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6004,19 +5982,19 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ST0044201N</t>
+          <t>ST0043935N</t>
         </is>
       </c>
       <c r="C115" s="1" t="n">
@@ -6029,11 +6007,11 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Z86192</t>
+          <t>S00462</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>256.8</v>
+        <v>13.91</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
@@ -6044,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>256.8</v>
+        <v>13.91</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6053,19 +6031,19 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ST0044202N</t>
+          <t>ST0043938N</t>
         </is>
       </c>
       <c r="C116" s="1" t="n">
@@ -6078,7 +6056,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SV0930</t>
+          <t>QL103</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6109,12 +6087,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ST0044204N</t>
+          <t>ST0043940N</t>
         </is>
       </c>
       <c r="C117" s="1" t="n">
@@ -6127,11 +6105,11 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>S09376</t>
+          <t>SV5823</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
@@ -6142,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6151,19 +6129,19 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ST0044205N</t>
+          <t>ST0043941N</t>
         </is>
       </c>
       <c r="C118" s="1" t="n">
@@ -6176,11 +6154,11 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>S01000</t>
+          <t>S00608</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -6191,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6200,19 +6178,19 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ST0044206N</t>
+          <t>ST0043942N</t>
         </is>
       </c>
       <c r="C119" s="1" t="n">
@@ -6225,7 +6203,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>S01935</t>
+          <t>S01158</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6256,12 +6234,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ST0044207N</t>
+          <t>ST0043947N</t>
         </is>
       </c>
       <c r="C120" s="1" t="n">
@@ -6274,7 +6252,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>S16502</t>
+          <t>S01543</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -6305,12 +6283,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ST00442/26</t>
+          <t>ST00439/26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ST0044208N</t>
+          <t>ST0043948N</t>
         </is>
       </c>
       <c r="C121" s="1" t="n">
@@ -6323,7 +6301,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>S50063</t>
+          <t>S00308</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -6359,7 +6337,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ST0044209N</t>
+          <t>ST0044201N</t>
         </is>
       </c>
       <c r="C122" s="1" t="n">
@@ -6372,11 +6350,11 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>S50430</t>
+          <t>Z86192</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>27.82</v>
+        <v>256.8</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
@@ -6387,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>27.82</v>
+        <v>256.8</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6396,7 +6374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6386,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ST0044210N</t>
+          <t>ST0044207N</t>
         </is>
       </c>
       <c r="C123" s="1" t="n">
@@ -6421,7 +6399,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>S50711</t>
+          <t>S16502</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -6457,7 +6435,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ST0044211N</t>
+          <t>ST0044208N</t>
         </is>
       </c>
       <c r="C124" s="1" t="n">
@@ -6470,11 +6448,11 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>S50411</t>
+          <t>S50063</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -6485,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6494,7 +6472,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6484,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ST0044212N</t>
+          <t>ST0044210N</t>
         </is>
       </c>
       <c r="C125" s="1" t="n">
@@ -6519,11 +6497,11 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>S50408</t>
+          <t>S50711</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
@@ -6534,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>27.82</v>
+        <v>13.91</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6543,7 +6521,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6533,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ST0044213N</t>
+          <t>ST0044211N</t>
         </is>
       </c>
       <c r="C126" s="1" t="n">
@@ -6568,11 +6546,11 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S50428</t>
+          <t>S50411</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>55.64</v>
+        <v>27.82</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
@@ -6583,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>55.64</v>
+        <v>27.82</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -6592,7 +6570,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
@@ -11156,16 +11134,16 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ST00449/26</t>
+          <t>ST00404/26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ST0044901N</t>
+          <t>ST0040405N</t>
         </is>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46273</v>
+        <v>46260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -11174,14 +11152,16 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>NG308</t>
+          <t>D20206</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>13.91</v>
+        <v>5.88</v>
       </c>
       <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
+      <c r="H220" t="n">
+        <v>5.69</v>
+      </c>
       <c r="I220" t="n">
         <v>0</v>
       </c>
@@ -11189,18 +11169,14 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>13.91</v>
+        <v>0.19</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2/60 SPUN POLYESTER YARN</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+          <t>210/2 CONTINOUS POLYESTER FILAMENT</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11210,7 +11186,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ST0040405N</t>
+          <t>ST0040408N</t>
         </is>
       </c>
       <c r="C221" s="1" t="n">
@@ -11223,7 +11199,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>D20206</t>
+          <t>D20209</t>
         </is>
       </c>
       <c r="F221" t="n">
@@ -11231,7 +11207,7 @@
       </c>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
-        <v>5.69</v>
+        <v>5.79</v>
       </c>
       <c r="I221" t="n">
         <v>0</v>
@@ -11240,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -11257,7 +11233,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ST0040408N</t>
+          <t>ST0040409N</t>
         </is>
       </c>
       <c r="C222" s="1" t="n">
@@ -11270,7 +11246,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>D20209</t>
+          <t>D20210</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -11278,16 +11254,16 @@
       </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="n">
-        <v>5.79</v>
+        <v>5.55</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="K222" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -11304,7 +11280,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ST0040409N</t>
+          <t>ST0040410N</t>
         </is>
       </c>
       <c r="C223" s="1" t="n">
@@ -11317,7 +11293,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>D20210</t>
+          <t>D20211</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -11325,16 +11301,16 @@
       </c>
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="I223" t="n">
         <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="K223" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -11351,7 +11327,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ST0040410N</t>
+          <t>ST0040413N</t>
         </is>
       </c>
       <c r="C224" s="1" t="n">
@@ -11364,7 +11340,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>D20211</t>
+          <t>D20214</t>
         </is>
       </c>
       <c r="F224" t="n">
@@ -11372,16 +11348,16 @@
       </c>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="n">
-        <v>5.7</v>
+        <v>5.53</v>
       </c>
       <c r="I224" t="n">
         <v>0</v>
       </c>
       <c r="J224" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -11398,7 +11374,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ST0040413N</t>
+          <t>ST0040414N</t>
         </is>
       </c>
       <c r="C225" s="1" t="n">
@@ -11411,7 +11387,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>D20214</t>
+          <t>D20215</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -11419,7 +11395,7 @@
       </c>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="n">
-        <v>5.53</v>
+        <v>5.74</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -11428,7 +11404,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>0.35</v>
+        <v>0.14</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -11445,7 +11421,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ST0040414N</t>
+          <t>ST0040415N</t>
         </is>
       </c>
       <c r="C226" s="1" t="n">
@@ -11458,7 +11434,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>D20215</t>
+          <t>D20216</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -11466,16 +11442,16 @@
       </c>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="n">
-        <v>5.74</v>
+        <v>5.27</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K226" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -11492,7 +11468,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ST0040415N</t>
+          <t>ST0040416N</t>
         </is>
       </c>
       <c r="C227" s="1" t="n">
@@ -11505,7 +11481,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>D20216</t>
+          <t>D20217</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -11513,16 +11489,16 @@
       </c>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="n">
-        <v>5.27</v>
+        <v>5.51</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -11539,7 +11515,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ST0040416N</t>
+          <t>ST0040417N</t>
         </is>
       </c>
       <c r="C228" s="1" t="n">
@@ -11552,7 +11528,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>D20217</t>
+          <t>D20218</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -11560,16 +11536,16 @@
       </c>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="n">
-        <v>5.51</v>
+        <v>5.16</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K228" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -11581,16 +11557,16 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ST00404/26</t>
+          <t>ST00383/26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ST0040417N</t>
+          <t>ST0038301N</t>
         </is>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46260</v>
+        <v>46250</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -11599,45 +11575,49 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>D20218</t>
+          <t>N-BLACK</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>5.88</v>
+        <v>105.84</v>
       </c>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="n">
-        <v>5.16</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>4.5</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="K229" t="n">
-        <v>0.72</v>
+        <v>9.08</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>210/2 CONTINOUS POLYESTER FILAMENT</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr"/>
+          <t>210/2 HI-TENACITY NYLON YARN</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ST00383/26</t>
+          <t>ST00395/26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ST0038301N</t>
+          <t>ST0039501N</t>
         </is>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -11646,24 +11626,26 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>N-BLACK</t>
+          <t>D20053</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="G230" t="inlineStr"/>
+        <v>0.98</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
       <c r="H230" t="n">
-        <v>96.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>96.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>9.08</v>
+        <v>0.98</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -11672,23 +11654,23 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ST00395/26</t>
+          <t>ST00422/26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ST0039501N</t>
+          <t>ST0042201N</t>
         </is>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -11697,51 +11679,45 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>D20053</t>
+          <t>D30057(PG0767)</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
+        <v>3.92</v>
+      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="K231" t="n">
-        <v>0.98</v>
+        <v>0.53</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>210/2 HI-TENACITY NYLON YARN</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ST00422/26</t>
+          <t>ST00446/26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ST0042201N</t>
+          <t>ST0044601N</t>
         </is>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -11750,24 +11726,24 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>D30057(PG0767)</t>
+          <t>N00904</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>3.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="n">
-        <v>3.39</v>
+        <v>9.02</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -11779,12 +11755,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ST00446/26</t>
+          <t>ST00448/26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ST0044601N</t>
+          <t>ST0044801N</t>
         </is>
       </c>
       <c r="C233" s="1" t="n">
@@ -11797,47 +11773,45 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>N00904</t>
+          <t>D30018</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>9.800000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
+      <c r="H233" t="n">
+        <v>0.92</v>
+      </c>
       <c r="I233" t="n">
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="K233" t="n">
-        <v>9.800000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>210/2 HI-TENACITY NYLON YARN</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ST00448/26</t>
+          <t>ST00280/26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ST0044801N</t>
+          <t>ST0028001N</t>
         </is>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46272</v>
+        <v>46220</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -11846,45 +11820,51 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>D30018</t>
+          <t>P-BLACK</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G234" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
       <c r="H234" t="n">
-        <v>0.92</v>
+        <v>74.64</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
+        <v>116.44</v>
       </c>
       <c r="K234" t="n">
-        <v>0.06</v>
+        <v>39.36</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>210/2 HI-TENACITY NYLON YARN</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr"/>
+          <t>210/3 CONTINOUS POLYESTER FILAMENT</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ST00280/26</t>
+          <t>ST00399/26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ST0028001N</t>
+          <t>ST0039901N</t>
         </is>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46220</v>
+        <v>46259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -11893,26 +11873,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P-BLACK</t>
+          <t>91394</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>114</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
-      <c r="H235" t="n">
-        <v>74.64</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>116.44</v>
+        <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>39.36</v>
+        <v>162</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -11921,7 +11897,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11909,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ST0039901N</t>
+          <t>ST0039902N</t>
         </is>
       </c>
       <c r="C236" s="1" t="n">
@@ -11946,11 +11922,11 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>91394</t>
+          <t>91230</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>162</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
@@ -11961,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>162</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -11977,12 +11953,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ST00399/26</t>
+          <t>ST00400/26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ST0039902N</t>
+          <t>ST0040004N</t>
         </is>
       </c>
       <c r="C237" s="1" t="n">
@@ -11995,11 +11971,11 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>91230</t>
+          <t>D20157</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>86.40000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
@@ -12010,7 +11986,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>86.40000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -12019,7 +11995,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
@@ -12031,7 +12007,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ST0040004N</t>
+          <t>ST0040005N</t>
         </is>
       </c>
       <c r="C238" s="1" t="n">
@@ -12044,14 +12020,16 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>D20157</t>
+          <t>D20159</t>
         </is>
       </c>
       <c r="F238" t="n">
         <v>6.84</v>
       </c>
       <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="n">
+        <v>5.48</v>
+      </c>
       <c r="I238" t="n">
         <v>0</v>
       </c>
@@ -12059,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>6.84</v>
+        <v>1.36</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -12068,23 +12046,23 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ST00400/26</t>
+          <t>ST00433/26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ST0040005N</t>
+          <t>ST0043302N</t>
         </is>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -12093,24 +12071,24 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>D20159</t>
+          <t>D20111</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>6.84</v>
+        <v>57</v>
       </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="n">
-        <v>5.48</v>
+        <v>54.32</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
+        <v>54.32</v>
       </c>
       <c r="K239" t="n">
-        <v>1.36</v>
+        <v>2.68</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -12119,23 +12097,23 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ST00433/26</t>
+          <t>ST00239/26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ST0043302N</t>
+          <t>ST0023901N</t>
         </is>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46269</v>
+        <v>46203</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -12144,49 +12122,51 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>D20111</t>
+          <t>N-BLACK</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>57</v>
-      </c>
-      <c r="G240" t="inlineStr"/>
+        <v>1026</v>
+      </c>
+      <c r="G240" t="n">
+        <v>192</v>
+      </c>
       <c r="H240" t="n">
-        <v>54.32</v>
+        <v>583.22</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>54.32</v>
+        <v>317.49</v>
       </c>
       <c r="K240" t="n">
-        <v>2.68</v>
+        <v>250.78</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>210/3 CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/3 HI-TENACITY NYLON</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ST00447/26</t>
+          <t>ST00412/26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ST0044701N</t>
+          <t>ST0041201N</t>
         </is>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -12195,14 +12175,18 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>D20040</t>
+          <t>N00731</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
       <c r="I241" t="n">
         <v>0</v>
       </c>
@@ -12210,32 +12194,32 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>54.72</v>
+        <v>0.91</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>210/3 CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/3 HI-TENACITY NYLON</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ST00447/26</t>
+          <t>ST00369/26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ST0044702N</t>
+          <t>ST0036901N</t>
         </is>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46272</v>
+        <v>46247</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -12244,47 +12228,45 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>D20143</t>
+          <t>P-BLACK</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>54.72</v>
+        <v>250</v>
       </c>
       <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
+      <c r="H242" t="n">
+        <v>249.58</v>
+      </c>
       <c r="I242" t="n">
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="K242" t="n">
-        <v>54.72</v>
+        <v>0.42</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>210/3 CONTINOUS POLYESTER FILAMENT</t>
-        </is>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
+          <t>210/3 PLY CF POLY BONDED</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ST00239/26</t>
+          <t>ST00376/26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ST0023901N</t>
+          <t>ST0037601N</t>
         </is>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46203</v>
+        <v>46247</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -12293,30 +12275,30 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>N-BLACK</t>
+          <t>P-BLACK</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>1026</v>
+        <v>250</v>
       </c>
       <c r="G243" t="n">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="H243" t="n">
-        <v>583.22</v>
+        <v>29.69</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
       </c>
       <c r="J243" t="n">
-        <v>236.28</v>
+        <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>250.78</v>
+        <v>122.31</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>210/3 HI-TENACITY NYLON</t>
+          <t>210/3 PLY CF POLY BONDED</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -12328,16 +12310,16 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ST00412/26</t>
+          <t>ST00436/26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ST0041201N</t>
+          <t>ST0043601N</t>
         </is>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46261</v>
+        <v>46270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -12346,18 +12328,14 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>N00731</t>
+          <t>P-BLACK</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G244" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" t="n">
-        <v>0</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
         <v>0</v>
       </c>
@@ -12365,32 +12343,32 @@
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>0.91</v>
+        <v>125</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>210/3 HI-TENACITY NYLON</t>
+          <t>210/3 PLY CF POLY BONDED</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ST00446/26</t>
+          <t>ST00274/26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ST0044602N</t>
+          <t>ST0027402N</t>
         </is>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46272</v>
+        <v>46217</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -12399,47 +12377,49 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>N00904</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>27.36</v>
+        <v>790.09</v>
       </c>
       <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
+      <c r="H245" t="n">
+        <v>62.25</v>
+      </c>
       <c r="I245" t="n">
         <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>62.25</v>
       </c>
       <c r="K245" t="n">
-        <v>27.36</v>
+        <v>727.84</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>210/3 HI-TENACITY NYLON</t>
+          <t>250/3 CONTINUOUS FILAMENT POLYSTER</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>more_than_48p</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ST00369/26</t>
+          <t>ST00307/26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ST0036901N</t>
+          <t>ST0030701N</t>
         </is>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46247</v>
+        <v>46229</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -12448,45 +12428,49 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P-BLACK</t>
+          <t>91276</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>250</v>
+        <v>240.84</v>
       </c>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="n">
-        <v>249.58</v>
+        <v>147.52</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>87.29000000000001</v>
+        <v>49.36</v>
       </c>
       <c r="K246" t="n">
-        <v>0.42</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>210/3 PLY CF POLY BONDED</t>
-        </is>
-      </c>
-      <c r="M246" t="inlineStr"/>
+          <t>250/3 CONTINUOUS FILAMENT POLYSTER</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>more_than_48p</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ST00376/26</t>
+          <t>ST00217/26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ST0037601N</t>
+          <t>ST0021701N</t>
         </is>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46247</v>
+        <v>46196</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -12495,51 +12479,49 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P-BLACK</t>
+          <t>92380</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>250</v>
-      </c>
-      <c r="G247" t="n">
-        <v>98</v>
-      </c>
+        <v>103.05</v>
+      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="n">
-        <v>29.69</v>
+        <v>55.3</v>
       </c>
       <c r="I247" t="n">
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>0</v>
+        <v>12.74</v>
       </c>
       <c r="K247" t="n">
-        <v>122.31</v>
+        <v>47.75</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>210/3 PLY CF POLY BONDED</t>
+          <t>420/3 CONTINOUS FILAMENT POLYESTER</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>7th</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ST00436/26</t>
+          <t>ST00399/26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ST0043601N</t>
+          <t>ST0039903N</t>
         </is>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46270</v>
+        <v>46259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -12548,11 +12530,11 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P-BLACK</t>
+          <t>91560</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>125</v>
+        <v>61.2</v>
       </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
@@ -12563,32 +12545,32 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>125</v>
+        <v>61.2</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>210/3 PLY CF POLY BONDED</t>
+          <t>420/3 CONTINOUS FILAMENT POLYESTER</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>7th</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ST00274/26</t>
+          <t>ST00247/26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ST0027402N</t>
+          <t>ST0024706N</t>
         </is>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46217</v>
+        <v>46205</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -12597,49 +12579,51 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>90002</t>
+          <t>D30056(PG9444)</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>790.09</v>
-      </c>
-      <c r="G249" t="inlineStr"/>
+        <v>49.6</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
       <c r="H249" t="n">
-        <v>62.25</v>
+        <v>25.44</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
       </c>
       <c r="J249" t="n">
-        <v>62.25</v>
+        <v>25.43</v>
       </c>
       <c r="K249" t="n">
-        <v>727.84</v>
+        <v>24.16</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>250/3 CONTINUOUS FILAMENT POLYSTER</t>
+          <t>420/3 HI TENACITY NYLON</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ST00307/26</t>
+          <t>ST00446/26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ST0030701N</t>
+          <t>ST0044603N</t>
         </is>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46229</v>
+        <v>46272</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -12648,15 +12632,15 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>91276</t>
+          <t>N00904</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>240.84</v>
+        <v>15.5</v>
       </c>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="n">
-        <v>147.52</v>
+        <v>13.04</v>
       </c>
       <c r="I250" t="n">
         <v>0</v>
@@ -12665,32 +12649,32 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>93.31999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>250/3 CONTINUOUS FILAMENT POLYSTER</t>
+          <t>420/3 HI TENACITY NYLON</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>more_than_48p</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ST00217/26</t>
+          <t>ST00362/26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ST0021701N</t>
+          <t>ST0036208N</t>
         </is>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46196</v>
+        <v>46245</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -12699,235 +12683,33 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>92380</t>
+          <t>91397</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>103.05</v>
-      </c>
-      <c r="G251" t="inlineStr"/>
+        <v>17.7</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
       <c r="H251" t="n">
-        <v>55.3</v>
+        <v>0</v>
       </c>
       <c r="I251" t="n">
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>12.74</v>
+        <v>0</v>
       </c>
       <c r="K251" t="n">
-        <v>47.75</v>
+        <v>17.7</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>420/3 CONTINOUS FILAMENT POLYESTER</t>
+          <t>840/3 PLY HT POLYESTER</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>ST00399/26</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>ST0039903N</t>
-        </is>
-      </c>
-      <c r="C252" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>KIRAN INDUSTRIES PVT LTD (STICH DIV SALES)</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>91560</t>
-        </is>
-      </c>
-      <c r="F252" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="n">
-        <v>0</v>
-      </c>
-      <c r="J252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K252" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>420/3 CONTINOUS FILAMENT POLYESTER</t>
-        </is>
-      </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>ST00247/26</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>ST0024706N</t>
-        </is>
-      </c>
-      <c r="C253" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>KIRAN INDUSTRIES PVT LTD (STICH DIV SALES)</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>D30056(PG9444)</t>
-        </is>
-      </c>
-      <c r="F253" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
-        <v>25.44</v>
-      </c>
-      <c r="I253" t="n">
-        <v>0</v>
-      </c>
-      <c r="J253" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="K253" t="n">
-        <v>24.16</v>
-      </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>420/3 HI TENACITY NYLON</t>
-        </is>
-      </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>ST00446/26</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>ST0044603N</t>
-        </is>
-      </c>
-      <c r="C254" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>KIRAN INDUSTRIES PVT LTD (STICH DIV SALES)</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>N00904</t>
-        </is>
-      </c>
-      <c r="F254" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="n">
-        <v>0</v>
-      </c>
-      <c r="J254" t="n">
-        <v>0</v>
-      </c>
-      <c r="K254" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>420/3 HI TENACITY NYLON</t>
-        </is>
-      </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>ST00362/26</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>ST0036208N</t>
-        </is>
-      </c>
-      <c r="C255" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>KIRAN INDUSTRIES PVT LTD (STICH DIV SALES)</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>91397</t>
-        </is>
-      </c>
-      <c r="F255" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" t="n">
-        <v>0</v>
-      </c>
-      <c r="K255" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>840/3 PLY HT POLYESTER</t>
-        </is>
-      </c>
-      <c r="M255" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
